--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/150.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/150.xlsx
@@ -426,13 +426,13 @@
         <v>-2.324324007556136</v>
       </c>
       <c r="E2">
-        <v>-17.36567646099769</v>
+        <v>-18.93618294617582</v>
       </c>
       <c r="F2">
-        <v>2.835769035206304</v>
+        <v>2.515946321394249</v>
       </c>
       <c r="G2">
-        <v>-6.825455515895458</v>
+        <v>-9.926950035998287</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.943572027019653</v>
       </c>
       <c r="E3">
-        <v>-19.02778491840298</v>
+        <v>-16.89884966096897</v>
       </c>
       <c r="F3">
-        <v>2.845467560758281</v>
+        <v>2.700779939980902</v>
       </c>
       <c r="G3">
-        <v>-7.333720261994224</v>
+        <v>-9.487266551291063</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.526179249740987</v>
       </c>
       <c r="E4">
-        <v>-20.09039587277683</v>
+        <v>-19.31623059879555</v>
       </c>
       <c r="F4">
-        <v>2.673508428345937</v>
+        <v>3.132437223375308</v>
       </c>
       <c r="G4">
-        <v>-8.46160988504176</v>
+        <v>-9.442918483246986</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.100289563950361</v>
       </c>
       <c r="E5">
-        <v>-20.7399782983331</v>
+        <v>-20.75595928310617</v>
       </c>
       <c r="F5">
-        <v>3.163974827134691</v>
+        <v>2.631031404665184</v>
       </c>
       <c r="G5">
-        <v>-7.20891600570924</v>
+        <v>-8.998484365690908</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.6688918861202793</v>
       </c>
       <c r="E6">
-        <v>-18.27835416945159</v>
+        <v>-19.55983532956417</v>
       </c>
       <c r="F6">
-        <v>2.860976255273493</v>
+        <v>2.804713541275351</v>
       </c>
       <c r="G6">
-        <v>-6.001017118068597</v>
+        <v>-9.07378934507271</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.2450616654066236</v>
       </c>
       <c r="E7">
-        <v>-20.93445361459251</v>
+        <v>-21.39228233676798</v>
       </c>
       <c r="F7">
-        <v>3.396674827724711</v>
+        <v>2.171784516553138</v>
       </c>
       <c r="G7">
-        <v>-6.610760016582643</v>
+        <v>-8.58466617328201</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.1625186502400236</v>
       </c>
       <c r="E8">
-        <v>-22.44032519025916</v>
+        <v>-21.96487617571984</v>
       </c>
       <c r="F8">
-        <v>3.567840384165173</v>
+        <v>2.828540701249476</v>
       </c>
       <c r="G8">
-        <v>-7.174552543011604</v>
+        <v>-8.372003348930306</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.5431391936018487</v>
       </c>
       <c r="E9">
-        <v>-21.32166531309237</v>
+        <v>-22.08219988031057</v>
       </c>
       <c r="F9">
-        <v>2.881423676244196</v>
+        <v>3.858350489061765</v>
       </c>
       <c r="G9">
-        <v>-5.983265972887025</v>
+        <v>-8.477659409816146</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.8904753526325144</v>
       </c>
       <c r="E10">
-        <v>-22.917264072747</v>
+        <v>-22.4549295189339</v>
       </c>
       <c r="F10">
-        <v>3.046179325721795</v>
+        <v>3.039926808565465</v>
       </c>
       <c r="G10">
-        <v>-5.891570482540291</v>
+        <v>-7.004509681932479</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.202866644670554</v>
       </c>
       <c r="E11">
-        <v>-23.02677163120049</v>
+        <v>-23.19470103282693</v>
       </c>
       <c r="F11">
-        <v>3.590859057554165</v>
+        <v>3.606700755765303</v>
       </c>
       <c r="G11">
-        <v>-6.044709698095898</v>
+        <v>-5.511824424821572</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.482124805822045</v>
       </c>
       <c r="E12">
-        <v>-23.02567121201662</v>
+        <v>-23.76348642513834</v>
       </c>
       <c r="F12">
-        <v>4.003800207849719</v>
+        <v>3.597312039621974</v>
       </c>
       <c r="G12">
-        <v>-6.188311231952865</v>
+        <v>-6.327797757704516</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.73325998840993</v>
       </c>
       <c r="E13">
-        <v>-24.66157791881353</v>
+        <v>-24.22952527068972</v>
       </c>
       <c r="F13">
-        <v>4.01251463292717</v>
+        <v>3.77783814771407</v>
       </c>
       <c r="G13">
-        <v>-4.88244005962303</v>
+        <v>-5.877894618917562</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.961895167401651</v>
       </c>
       <c r="E14">
-        <v>-25.31894931966299</v>
+        <v>-25.06515099390311</v>
       </c>
       <c r="F14">
-        <v>4.638624537189537</v>
+        <v>3.893257891415736</v>
       </c>
       <c r="G14">
-        <v>-6.171026873692329</v>
+        <v>-5.005738017687646</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.175585616768077</v>
       </c>
       <c r="E15">
-        <v>-25.50497903189809</v>
+        <v>-26.90768744119601</v>
       </c>
       <c r="F15">
-        <v>4.534947729789956</v>
+        <v>3.672801161039092</v>
       </c>
       <c r="G15">
-        <v>-4.795829567224618</v>
+        <v>-6.146730779979618</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.383732702532591</v>
       </c>
       <c r="E16">
-        <v>-26.22999224900012</v>
+        <v>-26.90172796940191</v>
       </c>
       <c r="F16">
-        <v>4.568970435757738</v>
+        <v>4.114359091631758</v>
       </c>
       <c r="G16">
-        <v>-5.506368645772853</v>
+        <v>-6.036155248422421</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.596849262592884</v>
       </c>
       <c r="E17">
-        <v>-27.78635178137829</v>
+        <v>-27.894220032241</v>
       </c>
       <c r="F17">
-        <v>5.333792118353688</v>
+        <v>4.108804059828585</v>
       </c>
       <c r="G17">
-        <v>-4.234152479395251</v>
+        <v>-4.675888502336822</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.822573305903252</v>
       </c>
       <c r="E18">
-        <v>-28.80593770420527</v>
+        <v>-27.1117812362477</v>
       </c>
       <c r="F18">
-        <v>4.796067359235222</v>
+        <v>4.744907388438325</v>
       </c>
       <c r="G18">
-        <v>-3.377274045829071</v>
+        <v>-5.030712773235908</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.064873134973815</v>
       </c>
       <c r="E19">
-        <v>-29.61413898882821</v>
+        <v>-27.33826380679332</v>
       </c>
       <c r="F19">
-        <v>4.717833028245225</v>
+        <v>4.638225264101387</v>
       </c>
       <c r="G19">
-        <v>-4.589526300853855</v>
+        <v>-4.54943890491882</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.32405677296756</v>
       </c>
       <c r="E20">
-        <v>-29.547300976712</v>
+        <v>-29.35260150098922</v>
       </c>
       <c r="F20">
-        <v>5.576758904534005</v>
+        <v>4.917897009899751</v>
       </c>
       <c r="G20">
-        <v>-3.627779716240183</v>
+        <v>-4.470419493441956</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.593802770484981</v>
       </c>
       <c r="E21">
-        <v>-29.23194483952885</v>
+        <v>-30.60018476891738</v>
       </c>
       <c r="F21">
-        <v>5.407581429860262</v>
+        <v>5.512255591612814</v>
       </c>
       <c r="G21">
-        <v>-2.963280394506591</v>
+        <v>-4.531505679732589</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.869173976362963</v>
       </c>
       <c r="E22">
-        <v>-29.82707689361689</v>
+        <v>-30.01972044214019</v>
       </c>
       <c r="F22">
-        <v>5.718035308346655</v>
+        <v>5.464473703084532</v>
       </c>
       <c r="G22">
-        <v>-3.292252615289508</v>
+        <v>-3.968537479142905</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.141456039902114</v>
       </c>
       <c r="E23">
-        <v>-30.88986672271405</v>
+        <v>-30.91095809040477</v>
       </c>
       <c r="F23">
-        <v>5.686908574819061</v>
+        <v>5.35216199387817</v>
       </c>
       <c r="G23">
-        <v>-2.981150719327577</v>
+        <v>-3.031034019513315</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.400164606321601</v>
       </c>
       <c r="E24">
-        <v>-30.33915447016725</v>
+        <v>-31.19788673200477</v>
       </c>
       <c r="F24">
-        <v>6.648936371529878</v>
+        <v>5.627653797762007</v>
       </c>
       <c r="G24">
-        <v>-4.577072028535117</v>
+        <v>-4.174880472060138</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.63630925592225</v>
       </c>
       <c r="E25">
-        <v>-30.66321433439314</v>
+        <v>-31.30224315127453</v>
       </c>
       <c r="F25">
-        <v>6.439889573759395</v>
+        <v>5.76541295358237</v>
       </c>
       <c r="G25">
-        <v>-2.324937693078782</v>
+        <v>-4.028051156302383</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.840854791905353</v>
       </c>
       <c r="E26">
-        <v>-30.42008056492132</v>
+        <v>-30.80670356180018</v>
       </c>
       <c r="F26">
-        <v>6.376736499704766</v>
+        <v>5.359955274403707</v>
       </c>
       <c r="G26">
-        <v>-2.8604018813282</v>
+        <v>-4.0120777740754</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.006622615339011</v>
       </c>
       <c r="E27">
-        <v>-30.62782883849721</v>
+        <v>-30.61378604059942</v>
       </c>
       <c r="F27">
-        <v>6.338724376325103</v>
+        <v>5.410717628847261</v>
       </c>
       <c r="G27">
-        <v>-3.341496980186167</v>
+        <v>-3.915164863958775</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.133108013461023</v>
       </c>
       <c r="E28">
-        <v>-30.24323686221078</v>
+        <v>-31.61468974390776</v>
       </c>
       <c r="F28">
-        <v>6.113037334167183</v>
+        <v>5.201568113518831</v>
       </c>
       <c r="G28">
-        <v>-3.673971758149633</v>
+        <v>-3.24945388255781</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.221678243183886</v>
       </c>
       <c r="E29">
-        <v>-30.54302184151856</v>
+        <v>-31.64520486600845</v>
       </c>
       <c r="F29">
-        <v>5.911081361364663</v>
+        <v>5.414823017695535</v>
       </c>
       <c r="G29">
-        <v>-3.329807443887001</v>
+        <v>-4.850317836255482</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.276224405712596</v>
       </c>
       <c r="E30">
-        <v>-29.5913449149106</v>
+        <v>-30.62821828726187</v>
       </c>
       <c r="F30">
-        <v>5.620024533982224</v>
+        <v>5.491891007382391</v>
       </c>
       <c r="G30">
-        <v>-3.917154501827877</v>
+        <v>-4.966918560694152</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.304632358388083</v>
       </c>
       <c r="E31">
-        <v>-28.9851339491628</v>
+        <v>-29.88803921070815</v>
       </c>
       <c r="F31">
-        <v>5.719763282748895</v>
+        <v>5.751065630165883</v>
       </c>
       <c r="G31">
-        <v>-4.724798502134015</v>
+        <v>-5.030044043036976</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.311942982878759</v>
       </c>
       <c r="E32">
-        <v>-29.77594136512227</v>
+        <v>-31.38450514586087</v>
       </c>
       <c r="F32">
-        <v>6.301910072209886</v>
+        <v>4.716810822870171</v>
       </c>
       <c r="G32">
-        <v>-3.791876837530777</v>
+        <v>-4.708662903175608</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.305116581757855</v>
       </c>
       <c r="E33">
-        <v>-28.08533522078671</v>
+        <v>-31.33211296582913</v>
       </c>
       <c r="F33">
-        <v>5.869063253225061</v>
+        <v>5.540314052280438</v>
       </c>
       <c r="G33">
-        <v>-3.047798622124185</v>
+        <v>-4.406333952892744</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.289939748680283</v>
       </c>
       <c r="E34">
-        <v>-29.29898889721241</v>
+        <v>-29.98284054982172</v>
       </c>
       <c r="F34">
-        <v>5.925559566830793</v>
+        <v>4.91159976090367</v>
       </c>
       <c r="G34">
-        <v>-4.994780111952659</v>
+        <v>-4.825508607984184</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.268402731295111</v>
       </c>
       <c r="E35">
-        <v>-27.07860563566751</v>
+        <v>-29.33165730870374</v>
       </c>
       <c r="F35">
-        <v>5.73297077261913</v>
+        <v>5.268975682554237</v>
       </c>
       <c r="G35">
-        <v>-4.402636073525379</v>
+        <v>-4.939702565815804</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.24236507293782</v>
       </c>
       <c r="E36">
-        <v>-28.95448976555289</v>
+        <v>-28.9320602337929</v>
       </c>
       <c r="F36">
-        <v>5.931245480683609</v>
+        <v>5.030931055481355</v>
       </c>
       <c r="G36">
-        <v>-5.151663554513181</v>
+        <v>-6.041289904553831</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.211644003109358</v>
       </c>
       <c r="E37">
-        <v>-26.91395937769663</v>
+        <v>-28.57148049093215</v>
       </c>
       <c r="F37">
-        <v>5.918009826321678</v>
+        <v>5.702894408958286</v>
       </c>
       <c r="G37">
-        <v>-5.568431442997571</v>
+        <v>-6.162379728743753</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.171753846510375</v>
       </c>
       <c r="E38">
-        <v>-27.28818341274249</v>
+        <v>-26.86548659191853</v>
       </c>
       <c r="F38">
-        <v>5.834013371677808</v>
+        <v>4.801957051469127</v>
       </c>
       <c r="G38">
-        <v>-6.575419942950923</v>
+        <v>-5.652777522247121</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.121427813440162</v>
       </c>
       <c r="E39">
-        <v>-25.71466549234926</v>
+        <v>-27.11206653011018</v>
       </c>
       <c r="F39">
-        <v>5.609489357353419</v>
+        <v>5.251270157686801</v>
       </c>
       <c r="G39">
-        <v>-4.534127631799691</v>
+        <v>-4.773774712841993</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.058171229547464</v>
       </c>
       <c r="E40">
-        <v>-24.7884340611904</v>
+        <v>-25.96066125739393</v>
       </c>
       <c r="F40">
-        <v>6.158995157674499</v>
+        <v>5.57779602052231</v>
       </c>
       <c r="G40">
-        <v>-4.279288457277674</v>
+        <v>-6.084376654747445</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.978601779170272</v>
       </c>
       <c r="E41">
-        <v>-25.9946519832955</v>
+        <v>-25.27031350882061</v>
       </c>
       <c r="F41">
-        <v>6.189860127102809</v>
+        <v>5.326128063142987</v>
       </c>
       <c r="G41">
-        <v>-5.556967023795074</v>
+        <v>-5.999163212566605</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.885496060488722</v>
       </c>
       <c r="E42">
-        <v>-24.1061243539807</v>
+        <v>-25.83358321979068</v>
       </c>
       <c r="F42">
-        <v>6.195584145856153</v>
+        <v>5.313081276548894</v>
       </c>
       <c r="G42">
-        <v>-6.034139126189005</v>
+        <v>-5.277166335906951</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.779019860954</v>
       </c>
       <c r="E43">
-        <v>-24.27108307665811</v>
+        <v>-25.15692051966855</v>
       </c>
       <c r="F43">
-        <v>6.140058678846502</v>
+        <v>5.709960382904166</v>
       </c>
       <c r="G43">
-        <v>-6.382911719842303</v>
+        <v>-6.273428668313065</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.660617323212334</v>
       </c>
       <c r="E44">
-        <v>-24.28983095904987</v>
+        <v>-23.6882503579749</v>
       </c>
       <c r="F44">
-        <v>6.155872212565945</v>
+        <v>4.99168466467152</v>
       </c>
       <c r="G44">
-        <v>-6.314578749366206</v>
+        <v>-6.052393474292546</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.533347429186477</v>
       </c>
       <c r="E45">
-        <v>-22.70359255516908</v>
+        <v>-23.01300507021717</v>
       </c>
       <c r="F45">
-        <v>5.878841302047706</v>
+        <v>5.31055309923555</v>
       </c>
       <c r="G45">
-        <v>-5.553209554608001</v>
+        <v>-5.987665687908716</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.398660176642317</v>
       </c>
       <c r="E46">
-        <v>-22.12662873879982</v>
+        <v>-22.66913086797071</v>
       </c>
       <c r="F46">
-        <v>6.319102009287588</v>
+        <v>5.420412840929626</v>
       </c>
       <c r="G46">
-        <v>-6.176029108002168</v>
+        <v>-6.746939307340563</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.258238657432122</v>
       </c>
       <c r="E47">
-        <v>-22.64529750926835</v>
+        <v>-20.3123590262628</v>
       </c>
       <c r="F47">
-        <v>5.41483627157398</v>
+        <v>5.618680922054883</v>
       </c>
       <c r="G47">
-        <v>-5.76293923561191</v>
+        <v>-6.363723797896688</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.1148920242756</v>
       </c>
       <c r="E48">
-        <v>-21.46672592098007</v>
+        <v>-21.96851706882201</v>
       </c>
       <c r="F48">
-        <v>5.97117444623335</v>
+        <v>5.506205196102766</v>
       </c>
       <c r="G48">
-        <v>-5.463146163212128</v>
+        <v>-5.97361573264005</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.967338059411187</v>
       </c>
       <c r="E49">
-        <v>-20.6540776748816</v>
+        <v>-22.0339852175509</v>
       </c>
       <c r="F49">
-        <v>5.808044053600044</v>
+        <v>5.716996535623545</v>
       </c>
       <c r="G49">
-        <v>-6.132164379606825</v>
+        <v>-6.477930997910465</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.81532304369969</v>
       </c>
       <c r="E50">
-        <v>-20.58000542553814</v>
+        <v>-21.69025592647269</v>
       </c>
       <c r="F50">
-        <v>5.901101190895734</v>
+        <v>5.213731860461539</v>
       </c>
       <c r="G50">
-        <v>-6.181269701590835</v>
+        <v>-6.166776133219905</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.657626673868519</v>
       </c>
       <c r="E51">
-        <v>-19.633536244039</v>
+        <v>-20.05445790305196</v>
       </c>
       <c r="F51">
-        <v>5.864503919040053</v>
+        <v>5.484516880762669</v>
       </c>
       <c r="G51">
-        <v>-7.070104831247598</v>
+        <v>-6.334584376060023</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.491603943184021</v>
       </c>
       <c r="E52">
-        <v>-20.52835817948066</v>
+        <v>-19.35642080561362</v>
       </c>
       <c r="F52">
-        <v>6.248684153110407</v>
+        <v>5.784778526725017</v>
       </c>
       <c r="G52">
-        <v>-6.502756778909459</v>
+        <v>-7.921057388298482</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.318161467819487</v>
       </c>
       <c r="E53">
-        <v>-18.08014286213586</v>
+        <v>-18.49803497203769</v>
       </c>
       <c r="F53">
-        <v>5.617126904807231</v>
+        <v>5.435762488903501</v>
       </c>
       <c r="G53">
-        <v>-6.414421492285086</v>
+        <v>-7.754586605856231</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.137459821742697</v>
       </c>
       <c r="E54">
-        <v>-18.64449487839376</v>
+        <v>-19.42331542365493</v>
       </c>
       <c r="F54">
-        <v>5.312052444234618</v>
+        <v>5.632218102151432</v>
       </c>
       <c r="G54">
-        <v>-6.66228203681032</v>
+        <v>-6.789052757145631</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.949375470268425</v>
       </c>
       <c r="E55">
-        <v>-18.70259519991217</v>
+        <v>-18.82396736026575</v>
       </c>
       <c r="F55">
-        <v>5.820356906675256</v>
+        <v>5.265968708882076</v>
       </c>
       <c r="G55">
-        <v>-6.933574622662515</v>
+        <v>-7.631325063792547</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.755672374225759</v>
       </c>
       <c r="E56">
-        <v>-17.83340442735393</v>
+        <v>-19.12619318706366</v>
       </c>
       <c r="F56">
-        <v>5.457092949525588</v>
+        <v>5.641282098272864</v>
       </c>
       <c r="G56">
-        <v>-6.960783996449785</v>
+        <v>-6.825601179899186</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.558266827498799</v>
       </c>
       <c r="E57">
-        <v>-16.00511003081515</v>
+        <v>-17.79055147781935</v>
       </c>
       <c r="F57">
-        <v>5.614370098090714</v>
+        <v>5.531831570075771</v>
       </c>
       <c r="G57">
-        <v>-7.97598595988607</v>
+        <v>-7.497300938180691</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.35898188084527</v>
       </c>
       <c r="E58">
-        <v>-17.79851253512483</v>
+        <v>-17.66458291634798</v>
       </c>
       <c r="F58">
-        <v>5.711721492002518</v>
+        <v>5.150351813738543</v>
       </c>
       <c r="G58">
-        <v>-7.941907204104812</v>
+        <v>-8.339622903010696</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.163052189051921</v>
       </c>
       <c r="E59">
-        <v>-17.35037927579978</v>
+        <v>-16.239404219024</v>
       </c>
       <c r="F59">
-        <v>5.236159079524932</v>
+        <v>5.092424081260774</v>
       </c>
       <c r="G59">
-        <v>-6.871333055978678</v>
+        <v>-8.332915737748133</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.973226437390286</v>
       </c>
       <c r="E60">
-        <v>-15.8884791827476</v>
+        <v>-17.75531542156566</v>
       </c>
       <c r="F60">
-        <v>6.006843946597897</v>
+        <v>5.232257469057747</v>
       </c>
       <c r="G60">
-        <v>-7.523196025388871</v>
+        <v>-8.609094688816292</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.792253105340617</v>
       </c>
       <c r="E61">
-        <v>-17.57860983731236</v>
+        <v>-16.20103898723102</v>
       </c>
       <c r="F61">
-        <v>5.180361908007163</v>
+        <v>5.255918955551312</v>
       </c>
       <c r="G61">
-        <v>-8.398868425981492</v>
+        <v>-8.432149340287786</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.622547276421956</v>
       </c>
       <c r="E62">
-        <v>-16.62676988564013</v>
+        <v>-15.51287849160341</v>
       </c>
       <c r="F62">
-        <v>4.984466271123525</v>
+        <v>4.669121711491004</v>
       </c>
       <c r="G62">
-        <v>-9.304809144439671</v>
+        <v>-8.354384625570306</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.465098208994649</v>
       </c>
       <c r="E63">
-        <v>-17.30633533760118</v>
+        <v>-15.65931575558944</v>
       </c>
       <c r="F63">
-        <v>5.255918955551312</v>
+        <v>5.063237384190535</v>
       </c>
       <c r="G63">
-        <v>-7.825534907308351</v>
+        <v>-7.920213199185968</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.321783055295032</v>
       </c>
       <c r="E64">
-        <v>-13.9981809200958</v>
+        <v>-15.80923088761337</v>
       </c>
       <c r="F64">
-        <v>4.851604423388513</v>
+        <v>4.90446586083076</v>
       </c>
       <c r="G64">
-        <v>-8.113052476848514</v>
+        <v>-8.133753318105578</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.194364546415821</v>
       </c>
       <c r="E65">
-        <v>-15.57695639881194</v>
+        <v>-16.35620262062984</v>
       </c>
       <c r="F65">
-        <v>4.111130115495645</v>
+        <v>5.064703594493491</v>
       </c>
       <c r="G65">
-        <v>-7.593174336997985</v>
+        <v>-8.257551168546623</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.082861440721481</v>
       </c>
       <c r="E66">
-        <v>-15.5648880155815</v>
+        <v>-14.41988147663808</v>
       </c>
       <c r="F66">
-        <v>4.429092316121014</v>
+        <v>4.608009734716873</v>
       </c>
       <c r="G66">
-        <v>-6.767782502055814</v>
+        <v>-8.191234320303943</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.9880464142979285</v>
       </c>
       <c r="E67">
-        <v>-14.93698792357396</v>
+        <v>-15.78004940110795</v>
       </c>
       <c r="F67">
-        <v>4.347107137531141</v>
+        <v>4.875945171152373</v>
       </c>
       <c r="G67">
-        <v>-7.387049840086343</v>
+        <v>-7.608240629747208</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.9104118984672328</v>
       </c>
       <c r="E68">
-        <v>-14.10880701162918</v>
+        <v>-14.05844132371587</v>
       </c>
       <c r="F68">
-        <v>4.339507694977858</v>
+        <v>4.75133883295366</v>
       </c>
       <c r="G68">
-        <v>-7.573009804118285</v>
+        <v>-7.954894474255373</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.8498964819867787</v>
       </c>
       <c r="E69">
-        <v>-15.72164114335701</v>
+        <v>-15.75488467104732</v>
       </c>
       <c r="F69">
-        <v>4.327085497405476</v>
+        <v>4.744872597007407</v>
       </c>
       <c r="G69">
-        <v>-6.291818748783717</v>
+        <v>-8.402466988982681</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.8082253165711858</v>
       </c>
       <c r="E70">
-        <v>-14.0699708185394</v>
+        <v>-14.6561047947742</v>
       </c>
       <c r="F70">
-        <v>4.627691744207389</v>
+        <v>4.783723028198704</v>
       </c>
       <c r="G70">
-        <v>-7.930217667805645</v>
+        <v>-8.02059225048221</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.7853759905733841</v>
       </c>
       <c r="E71">
-        <v>-15.97312994737299</v>
+        <v>-14.78990761627884</v>
       </c>
       <c r="F71">
-        <v>4.011726027159705</v>
+        <v>4.127217010458012</v>
       </c>
       <c r="G71">
-        <v>-6.751140389629898</v>
+        <v>-7.047874517951392</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.7810117933817545</v>
       </c>
       <c r="E72">
-        <v>-14.984831251465</v>
+        <v>-16.93825191330971</v>
       </c>
       <c r="F72">
-        <v>4.436058885978557</v>
+        <v>4.079274418653588</v>
       </c>
       <c r="G72">
-        <v>-7.111880605407661</v>
+        <v>-8.041723462659377</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.795618981571721</v>
       </c>
       <c r="E73">
-        <v>-15.33773070240874</v>
+        <v>-16.11803205867042</v>
       </c>
       <c r="F73">
-        <v>3.822415911128322</v>
+        <v>4.104243068908771</v>
       </c>
       <c r="G73">
-        <v>-7.298512610184074</v>
+        <v>-7.154785275596616</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.8293795727014869</v>
       </c>
       <c r="E74">
-        <v>-15.35510192870217</v>
+        <v>-16.63032020926214</v>
       </c>
       <c r="F74">
-        <v>3.613223320694947</v>
+        <v>4.433277228239956</v>
       </c>
       <c r="G74">
-        <v>-5.653363488807573</v>
+        <v>-6.229107084633303</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.8828500142011928</v>
       </c>
       <c r="E75">
-        <v>-14.58078721507863</v>
+        <v>-17.30194271781374</v>
       </c>
       <c r="F75">
-        <v>3.986798795274662</v>
+        <v>4.122763707300562</v>
       </c>
       <c r="G75">
-        <v>-5.960039185383498</v>
+        <v>-8.300747166743033</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.9569675654346395</v>
       </c>
       <c r="E76">
-        <v>-15.83904183200587</v>
+        <v>-15.78351368372381</v>
       </c>
       <c r="F76">
-        <v>3.833144925729382</v>
+        <v>4.166017739605141</v>
       </c>
       <c r="G76">
-        <v>-5.648007026125032</v>
+        <v>-7.152709563543493</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.050498707175415</v>
       </c>
       <c r="E77">
-        <v>-16.23009367646423</v>
+        <v>-18.17539025593919</v>
       </c>
       <c r="F77">
-        <v>3.692585888087556</v>
+        <v>4.020959010231308</v>
       </c>
       <c r="G77">
-        <v>-6.167507763784084</v>
+        <v>-6.372000161744865</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.163437432125325</v>
       </c>
       <c r="E78">
-        <v>-17.31669195765672</v>
+        <v>-17.16409144054624</v>
       </c>
       <c r="F78">
-        <v>3.366325102820943</v>
+        <v>3.457703967758562</v>
       </c>
       <c r="G78">
-        <v>-5.296201972757761</v>
+        <v>-7.52338141593907</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.295124916778198</v>
       </c>
       <c r="E79">
-        <v>-16.17839208871866</v>
+        <v>-17.73549429083409</v>
       </c>
       <c r="F79">
-        <v>3.742703772691732</v>
+        <v>4.065730611617815</v>
       </c>
       <c r="G79">
-        <v>-5.648698930142739</v>
+        <v>-6.484750721721364</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.444017430040907</v>
       </c>
       <c r="E80">
-        <v>-17.84536412720819</v>
+        <v>-17.7543916128681</v>
       </c>
       <c r="F80">
-        <v>3.239591517131841</v>
+        <v>3.738896596108465</v>
       </c>
       <c r="G80">
-        <v>-5.460229572592031</v>
+        <v>-6.325880951837278</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.608596418679724</v>
       </c>
       <c r="E81">
-        <v>-18.19835867610609</v>
+        <v>-18.28758319947922</v>
       </c>
       <c r="F81">
-        <v>3.129751656255432</v>
+        <v>3.750268423814097</v>
       </c>
       <c r="G81">
-        <v>-5.588956825341051</v>
+        <v>-6.768798839536371</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.786543096687484</v>
       </c>
       <c r="E82">
-        <v>-19.70189355918479</v>
+        <v>-19.41885034828337</v>
       </c>
       <c r="F82">
-        <v>3.601757059105396</v>
+        <v>3.703629682301679</v>
       </c>
       <c r="G82">
-        <v>-3.865639102691278</v>
+        <v>-5.679950480033459</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.973985625225615</v>
       </c>
       <c r="E83">
-        <v>-19.86151321100715</v>
+        <v>-19.50629518137148</v>
       </c>
       <c r="F83">
-        <v>3.458658247006587</v>
+        <v>3.866958883111657</v>
       </c>
       <c r="G83">
-        <v>-3.631431247969998</v>
+        <v>-5.725907473209622</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.170043298621714</v>
       </c>
       <c r="E84">
-        <v>-21.05678581143571</v>
+        <v>-21.0745510149678</v>
       </c>
       <c r="F84">
-        <v>3.25383280952077</v>
+        <v>3.024532428751839</v>
       </c>
       <c r="G84">
-        <v>-4.502770144451715</v>
+        <v>-5.129572284129624</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.373030605721344</v>
       </c>
       <c r="E85">
-        <v>-22.00558262857479</v>
+        <v>-21.13093504483731</v>
       </c>
       <c r="F85">
-        <v>3.859720608745996</v>
+        <v>3.638480242806303</v>
       </c>
       <c r="G85">
-        <v>-3.748588144059267</v>
+        <v>-6.029242829336423</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.581236753260968</v>
       </c>
       <c r="E86">
-        <v>-22.8457051264778</v>
+        <v>-23.9342053667535</v>
       </c>
       <c r="F86">
-        <v>3.531914089905758</v>
+        <v>3.481403559152656</v>
       </c>
       <c r="G86">
-        <v>-3.488673903225546</v>
+        <v>-4.241256910122526</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.79400716274915</v>
       </c>
       <c r="E87">
-        <v>-22.70640926600186</v>
+        <v>-23.51259537969138</v>
       </c>
       <c r="F87">
-        <v>3.166488093834785</v>
+        <v>3.12713235852778</v>
       </c>
       <c r="G87">
-        <v>-3.823707732890869</v>
+        <v>-5.218817970777297</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.008628518445108</v>
       </c>
       <c r="E88">
-        <v>-23.55917526333428</v>
+        <v>-25.34438575816408</v>
       </c>
       <c r="F88">
-        <v>3.054274131981952</v>
+        <v>3.06112638713791</v>
       </c>
       <c r="G88">
-        <v>-3.844481406149796</v>
+        <v>-4.068486159519042</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.223706826981932</v>
       </c>
       <c r="E89">
-        <v>-25.43722853226933</v>
+        <v>-26.55342944804996</v>
       </c>
       <c r="F89">
-        <v>2.724517636275525</v>
+        <v>2.606435519741261</v>
       </c>
       <c r="G89">
-        <v>-4.481284703901844</v>
+        <v>-5.384034056460165</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.438954341219211</v>
       </c>
       <c r="E90">
-        <v>-27.67622382198576</v>
+        <v>-27.49378066116473</v>
       </c>
       <c r="F90">
-        <v>3.309939790447186</v>
+        <v>3.094292561211196</v>
       </c>
       <c r="G90">
-        <v>-3.284141778718294</v>
+        <v>-4.327801191610154</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.652734747076415</v>
       </c>
       <c r="E91">
-        <v>-28.88665322491799</v>
+        <v>-27.33227263568117</v>
       </c>
       <c r="F91">
-        <v>3.567591873944333</v>
+        <v>2.929757257462742</v>
       </c>
       <c r="G91">
-        <v>-3.833705580419468</v>
+        <v>-5.073637306698099</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.863362643082312</v>
       </c>
       <c r="E92">
-        <v>-31.13641269735065</v>
+        <v>-30.24986881239501</v>
       </c>
       <c r="F92">
-        <v>3.199959107112301</v>
+        <v>3.130745697138791</v>
       </c>
       <c r="G92">
-        <v>-3.38591125914103</v>
+        <v>-5.056439022621585</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.06889168113891</v>
       </c>
       <c r="E93">
-        <v>-32.5506573941831</v>
+        <v>-31.6503741190882</v>
       </c>
       <c r="F93">
-        <v>2.840918166982106</v>
+        <v>2.357921985431798</v>
       </c>
       <c r="G93">
-        <v>-3.972622692338366</v>
+        <v>-4.574910242297973</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.26318863708565</v>
       </c>
       <c r="E94">
-        <v>-33.05859368125345</v>
+        <v>-33.1516696717701</v>
       </c>
       <c r="F94">
-        <v>2.230212582942198</v>
+        <v>2.710335986339597</v>
       </c>
       <c r="G94">
-        <v>-3.108391537129465</v>
+        <v>-4.959489696504028</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.445058479803436</v>
       </c>
       <c r="E95">
-        <v>-35.54509951057011</v>
+        <v>-36.30176449674875</v>
       </c>
       <c r="F95">
-        <v>2.586667360040854</v>
+        <v>2.127331008249306</v>
       </c>
       <c r="G95">
-        <v>-5.248000429705972</v>
+        <v>-4.138610135131883</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.610346049716409</v>
       </c>
       <c r="E96">
-        <v>-38.12507983611609</v>
+        <v>-39.11754699234815</v>
       </c>
       <c r="F96">
-        <v>2.783383080653263</v>
+        <v>1.897104512724044</v>
       </c>
       <c r="G96">
-        <v>-3.481145722669244</v>
+        <v>-5.81439835547434</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.755792066316018</v>
       </c>
       <c r="E97">
-        <v>-38.90642953411055</v>
+        <v>-39.89543240772673</v>
       </c>
       <c r="F97">
-        <v>1.780228499128257</v>
+        <v>1.944581562048095</v>
       </c>
       <c r="G97">
-        <v>-5.032662684558539</v>
+        <v>-6.118670595988756</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.877376966155932</v>
       </c>
       <c r="E98">
-        <v>-40.9597053120614</v>
+        <v>-41.39109680298009</v>
       </c>
       <c r="F98">
-        <v>2.096908387014091</v>
+        <v>1.315603849837236</v>
       </c>
       <c r="G98">
-        <v>-3.945376902550164</v>
+        <v>-5.971046749301575</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.973721717833875</v>
       </c>
       <c r="E99">
-        <v>-43.14238449901844</v>
+        <v>-44.50529667873695</v>
       </c>
       <c r="F99">
-        <v>1.512190345134809</v>
+        <v>0.6885603755119141</v>
       </c>
       <c r="G99">
-        <v>-5.478020444320074</v>
+        <v>-6.674110616022136</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.03560798398322</v>
       </c>
       <c r="E100">
-        <v>-46.67548407014382</v>
+        <v>-45.98630693210149</v>
       </c>
       <c r="F100">
-        <v>1.744789284901688</v>
+        <v>1.080695421751352</v>
       </c>
       <c r="G100">
-        <v>-5.145251027803613</v>
+        <v>-6.412805946061922</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.068587148284447</v>
       </c>
       <c r="E101">
-        <v>-46.69971819879587</v>
+        <v>-48.09956234828394</v>
       </c>
       <c r="F101">
-        <v>1.08157349119832</v>
+        <v>0.5095824860956502</v>
       </c>
       <c r="G101">
-        <v>-6.178574917521868</v>
+        <v>-6.20458918436946</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.057811072938946</v>
       </c>
       <c r="E102">
-        <v>-50.85680073191217</v>
+        <v>-49.73282782261587</v>
       </c>
       <c r="F102">
-        <v>0.967474165136716</v>
+        <v>-0.4203460737566861</v>
       </c>
       <c r="G102">
-        <v>-6.467476295097446</v>
+        <v>-7.143079186569753</v>
       </c>
     </row>
   </sheetData>
